--- a/out/Attention_Base_repeat_2_000006.xlsx
+++ b/out/Attention_Base_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>15.28973846592426</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.1742763026941591</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC44" t="n">
-        <v>-5.113152705365792e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.06581025827228758</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1317450612097988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.01519829364927153</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.05056083309596241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.05056083309596241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.05049346794002224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2069603280649097</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4648262304554276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.03959946472118359</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3367629381030302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0693624355333953</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4359076316691118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0379851555764479</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4424561980214322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01568861925315071</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4358079836439788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0195461828627473</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4592153450370701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01176817925537965</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.463193604961955</v>
+        <v>-0.0002105096904070815</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.008945698889074837</v>
+        <v>0.1001158840515743</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4693134159177437</v>
+        <v>0.2004885115388017</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.003953926535315225</v>
+        <v>0.03313146267498045</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4682690490630101</v>
+        <v>0.1663761914939028</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003137675919314173</v>
+        <v>0.05465099940968746</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.470587744349756</v>
+        <v>0.2424999954696023</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001553422204039044</v>
+        <v>0.02690233005959708</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4705549303812415</v>
+        <v>0.241572440664039</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0008997614318907874</v>
+        <v>0.01761233320805713</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.470803118930717</v>
+        <v>0.249861056100012</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0004488353163182084</v>
+        <v>0.008804925880546726</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.470797553875112</v>
+        <v>0.2498375686397012</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002192225566657728</v>
+        <v>0.004311784747824878</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4707868779063155</v>
+        <v>0.2496468279895927</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001251684583382067</v>
+        <v>0.002744186263317278</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4708178743160781</v>
+        <v>0.2508200202391262</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>3.740743216546624e-05</v>
+        <v>0.0006641675920707707</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4707696475226011</v>
+        <v>0.2493995752716772</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.745791147271043e-05</v>
+        <v>0.0003339927056578094</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.470764896024337</v>
+        <v>0.2494025163146912</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.230980650542531e-06</v>
+        <v>0.0001970924866121431</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4707618871525233</v>
+        <v>0.2494612324166505</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>8.996498865445193e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4707565006683657</v>
+        <v>0.2494438173308142</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>6.404330627387715e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4707531160499149</v>
+        <v>0.2494818458767734</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>2.28875571533536e-05</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4707474486196411</v>
+        <v>0.2494634972713001</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>1.274456273393902e-05</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4707478291546989</v>
+        <v>0.2494660711697619</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>5.012516614148175e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4707480574757336</v>
+        <v>0.2494633346088356</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>-8.153199214519686e-07</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4707481474203835</v>
+        <v>0.2494587762077095</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0</v>
+        <v>-3.764564025272377e-06</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4707472894867987</v>
+        <v>0.2494511993742872</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0</v>
+        <v>-3.536516975836643e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4707475178078334</v>
+        <v>0.2494466527097032</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4707467221436217</v>
+        <v>0.2494458570454915</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4707467844129947</v>
+        <v>0.2494459193148646</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4707468120882716</v>
+        <v>0.2494459469901414</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4707469643022949</v>
+        <v>0.2494460992041647</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4707466183613331</v>
+        <v>0.249445753263203</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4707466944683448</v>
+        <v>0.2494458293702146</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4707468605200064</v>
+        <v>0.2494459954218762</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4707472202986064</v>
+        <v>0.2494463552004763</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4707472410550642</v>
+        <v>0.2494463759569339</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4707473448373526</v>
+        <v>0.2494464797392224</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4707475731583873</v>
+        <v>0.2494467080602571</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4707474486196411</v>
+        <v>0.2494465835215109</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.470747476294918</v>
+        <v>0.2494466111967878</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.470747531645472</v>
+        <v>0.2494466665473417</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4707477945606026</v>
+        <v>0.2494469294624724</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4707477115347719</v>
+        <v>0.2494468464366416</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.470747503970195</v>
+        <v>0.2494466388720649</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4707475178078334</v>
+        <v>0.2494466527097032</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4707476561842181</v>
+        <v>0.2494467910860879</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4707473725126295</v>
+        <v>0.2494465074144993</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4707471995421487</v>
+        <v>0.2494463344440185</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4707470957598602</v>
+        <v>0.2494462306617301</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4707472410550642</v>
+        <v>0.2494463759569339</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4707474832137374</v>
+        <v>0.2494466181156072</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4707473102432564</v>
+        <v>0.2494464451451262</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4707470127340295</v>
+        <v>0.2494461476358993</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4257236973058409</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4707469988963909</v>
+        <v>0.2494461337982607</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4707466321989717</v>
+        <v>0.2494457671008415</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4707466321989717</v>
+        <v>0.2494457671008415</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4707465699295986</v>
+        <v>0.2494457048314684</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4707464661473101</v>
+        <v>0.2494456010491799</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4707462931768294</v>
+        <v>0.2494454280786992</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4707463416085639</v>
+        <v>0.2494454765104337</v>
       </c>
     </row>
     <row r="108">
@@ -86793,21 +86793,21 @@
         <v>0</v>
       </c>
       <c r="IY108" t="n">
-        <v>0</v>
+        <v>-5.070651672040668e-06</v>
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4707459818299639</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4707459403170485</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4707459956676022</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4707460510181561</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4707460925310715</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4707458226971214</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4707458780476754</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4707460233428792</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.470745988748783</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4707459749111444</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4707460648557947</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4707463831214793</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4707462032321791</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4707462447450946</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4707460579369753</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4707461271251678</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4707459264794099</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4707459679923253</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.873712549958921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4707459956676022</v>
+        <v>0.2494401152683538</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_2_000006.xlsx
+++ b/out/Attention_Base_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>15.28973846592426</v>
+        <v>1.356894732352283</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4257236973058409</v>
+        <v>0.8625263098030441</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.1742763026941591</v>
+        <v>0.07378946470456628</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4257236973058409</v>
+        <v>0.07378946470456628</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC44" t="n">
-        <v>-5.113152705365792e-05</v>
+        <v>-8.551245649962221e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.06581025827228758</v>
+        <v>0.1100611926148017</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1317450612097988</v>
+        <v>0.2203306739485385</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.01519829364927153</v>
+        <v>-0.02541765324530227</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.05056083309596241</v>
+        <v>0.08455802691299981</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.05056083309596241</v>
+        <v>0.08455802691299981</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.05049346794002224</v>
+        <v>0.08446110660966952</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2069603280649097</v>
+        <v>0.29775997044978</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4648262304554276</v>
+        <v>0.68057428238972</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.03959946472118359</v>
+        <v>0.05697301528934852</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3367629381030302</v>
+        <v>0.4963256194686482</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0693624355333953</v>
+        <v>0.09979363949121509</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4359076316691118</v>
+        <v>0.6389681222425574</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0379851555764479</v>
+        <v>0.05465062853537697</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4424561980214322</v>
+        <v>0.6483897652474754</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01568861925315071</v>
+        <v>0.0225715054779191</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4358079836439788</v>
+        <v>0.6388247737476923</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0195461828627473</v>
+        <v>0.02812264928947665</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4592153450370701</v>
+        <v>0.6725019618182457</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01176817925537965</v>
+        <v>0.01693346754142128</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.463193604961955</v>
+        <v>0.6782271636049944</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.008945698889074837</v>
+        <v>0.01287308302627226</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4693134159177437</v>
+        <v>0.6870335307379781</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.003953926535315225</v>
+        <v>0.005691022762974615</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4682690490630101</v>
+        <v>0.6855334095433091</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003137675919314173</v>
+        <v>0.004514803569350721</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.470587744349756</v>
+        <v>0.6888703533264942</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001553422204039044</v>
+        <v>0.002236326315921322</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4705549303812415</v>
+        <v>0.6888253512144734</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0008997614318907874</v>
+        <v>0.001298321934042034</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.470803118930717</v>
+        <v>0.689184484950599</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0004488353163182084</v>
+        <v>0.0006466609670210172</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.470797553875112</v>
+        <v>0.6891786735887045</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002192225566657728</v>
+        <v>0.0003169605941867507</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4707868779063155</v>
+        <v>0.6891655234796633</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001251684583382067</v>
+        <v>0.0001819085555625532</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4708178743160781</v>
+        <v>0.6892122106321431</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>3.740743216546624e-05</v>
+        <v>5.749516319121342e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4707696475226011</v>
+        <v>0.6891451393738697</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.745791147271043e-05</v>
+        <v>2.644107606179461e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.470764896024337</v>
+        <v>0.6891404872762998</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.230980650542531e-06</v>
+        <v>1.212337291075954e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4707618871525233</v>
+        <v>0.6891382748557606</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4707565006683657</v>
+        <v>0.6891327331830303</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4707531160499149</v>
+        <v>0.6891298846103283</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4707474486196411</v>
+        <v>0.6891242171800547</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4707478291546989</v>
+        <v>0.6891245977151124</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4707480574757336</v>
+        <v>0.6891248260361471</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4707481474203835</v>
+        <v>0.6891249159807971</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4707472894867987</v>
+        <v>0.6891240580472122</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4707475178078334</v>
+        <v>0.6891242863682469</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4707467221436217</v>
+        <v>0.6891234907040351</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4707467844129947</v>
+        <v>0.6891235529734082</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4707468120882716</v>
+        <v>0.6891235806486851</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4707469643022949</v>
+        <v>0.6891237328627083</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4707466183613331</v>
+        <v>0.6891233869217467</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4707466944683448</v>
+        <v>0.6891234630287583</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4707468605200064</v>
+        <v>0.6891236290804199</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4707472202986064</v>
+        <v>0.6891239888590199</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4707472410550642</v>
+        <v>0.6891240096154776</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4707473448373526</v>
+        <v>0.6891241133977661</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4707475731583873</v>
+        <v>0.6891243417188009</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4707474486196411</v>
+        <v>0.6891242171800547</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.470747476294918</v>
+        <v>0.6891242448553315</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.470747531645472</v>
+        <v>0.6891243002058854</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4707477945606026</v>
+        <v>0.6891245631210161</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4707477115347719</v>
+        <v>0.6891244800951853</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.470747503970195</v>
+        <v>0.6891242725306086</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4707475178078334</v>
+        <v>0.6891242863682469</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4707476561842181</v>
+        <v>0.6891244247446316</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4707473725126295</v>
+        <v>0.689124141073043</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4707471995421487</v>
+        <v>0.6891239681025623</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4707470957598602</v>
+        <v>0.6891238643202737</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4707472410550642</v>
+        <v>0.6891240096154776</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4707474832137374</v>
+        <v>0.6891242517741509</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4707473102432564</v>
+        <v>0.6891240788036699</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4707470127340295</v>
+        <v>0.689123781294443</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4707469988963909</v>
+        <v>0.6891237674568044</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4707466321989717</v>
+        <v>0.6891234007593852</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4707466321989717</v>
+        <v>0.6891234007593852</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4707465699295986</v>
+        <v>0.6891233384900121</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4707464661473101</v>
+        <v>0.6891232347077236</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4707462931768294</v>
+        <v>0.6891230617372428</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4707463416085639</v>
+        <v>0.6891231101689774</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4707459818299639</v>
+        <v>0.6891227503903774</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4707459403170485</v>
+        <v>0.689122708877462</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4707459956676022</v>
+        <v>0.6891227642280157</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4707460510181561</v>
+        <v>0.6891228195785696</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4707460925310715</v>
+        <v>0.689122861091485</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4707458226971214</v>
+        <v>0.6891225912575349</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4707458780476754</v>
+        <v>0.6891226466080889</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4707460233428792</v>
+        <v>0.6891227919032927</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.470745988748783</v>
+        <v>0.6891227573091965</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4707459749111444</v>
+        <v>0.689122743471558</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4707460648557947</v>
+        <v>0.6891228334162082</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4707463831214793</v>
+        <v>0.6891231516818928</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4707462032321791</v>
+        <v>0.6891229717925926</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4707462447450946</v>
+        <v>0.6891230133055081</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4707460579369753</v>
+        <v>0.6891228264973888</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4707461271251678</v>
+        <v>0.6891228956855813</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4707459264794099</v>
+        <v>0.6891226950398234</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4707459679923253</v>
+        <v>0.6891227365527388</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4257236973058409</v>
+        <v>-0.1262105352954337</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4707459956676022</v>
+        <v>0.6891227642280157</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_2_000006.xlsx
+++ b/out/Attention_Base_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>8.241180330514908e-05</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.356894732352283</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.000327087938785553</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8625263098030441</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.001396192237734795</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.07378946470456628</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.003049794584512711</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.07378946470456628</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.002837319858372211</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.003063301555812359</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0021605109795928</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.002704069018363953</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.00325984600931406</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.003132890909910202</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.002515483647584915</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001699982210993767</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.001658812165260315</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001198060810565948</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0006913943216204643</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0001913430169224739</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-1.337099820375443e-05</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0001187743619084358</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0005893530324101448</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0006479648873209953</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.000592520460486412</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0002911165356636047</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-8.61017033457756e-05</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0002924781292676926</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.000177307054400444</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0005324780941009521</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.001746313646435738</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.002363137900829315</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.002596443518996239</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.002775724977254868</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.002719287760555744</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.002512095496058464</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.002399458549916744</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.002842067740857601</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.003083145245909691</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.00321683008223772</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.003458154387772083</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.00351809523999691</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.003599677234888077</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.003825950436294079</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.004306034184992313</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.004985309205949306</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.006093640811741352</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-8.551245649962221e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1100611926148017</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.007266303524374962</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2203306739485385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.02541765324530227</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.007855907082557678</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.08455802691299981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.008300975896418095</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.08455802691299981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.008966740220785141</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.08446110660966952</v>
+        <v>-1.572706125420518e-05</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.29775997044978</v>
+        <v>0.0483169334537267</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.009462062269449234</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.68057428238972</v>
+        <v>0.09671435015372233</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.05697301528934852</v>
+        <v>0.00924483870115754</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.009964851662516594</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4963256194686482</v>
+        <v>0.06681670935983816</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.09979363949121509</v>
+        <v>0.01619342928458149</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01073383446782827</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6389681222425574</v>
+        <v>0.08996313684407575</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.05465062853537697</v>
+        <v>0.008866366249509762</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01133760530501604</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6483897652474754</v>
+        <v>0.09149022721617087</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0225715054779191</v>
+        <v>0.003659054835664152</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01187704689800739</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6388247737476923</v>
+        <v>0.08993453340209276</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02812264928947665</v>
+        <v>0.004559387025061533</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.012750294059515</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6725019618182457</v>
+        <v>0.09539572624475672</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01693346754142128</v>
+        <v>0.002743335502610705</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0139791164547205</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6782271636049944</v>
+        <v>0.09632073378365487</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01287308302627226</v>
+        <v>0.002084454598152154</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0147917028516531</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6870335307379781</v>
+        <v>0.09774598404177814</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.005691022762974615</v>
+        <v>0.0009199679821571501</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01645193621516228</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6855334095433091</v>
+        <v>0.09749819371384895</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.004514803569350721</v>
+        <v>0.0007289636376568415</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.01736450754106045</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6888703533264942</v>
+        <v>0.09803588659381936</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.002236326315921322</v>
+        <v>0.0003577146381792318</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.01668618060648441</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6888253512144734</v>
+        <v>0.09802439228128665</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001298321934042034</v>
+        <v>0.0002073716544309565</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01987412199378014</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.689184484950599</v>
+        <v>0.09807872657311079</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0006466609670210172</v>
+        <v>9.973122684266348e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.02316883951425552</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6891786735887045</v>
+        <v>0.0980735961756634</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0003169605941867507</v>
+        <v>4.674366692287064e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0246836319565773</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6891655234796633</v>
+        <v>0.0980672517426142</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001819085555625532</v>
+        <v>2.503887500112463e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.02528585121035576</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6892122106321431</v>
+        <v>0.09807102216729405</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>5.749516319121342e-05</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.02577603980898857</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6891451393738697</v>
+        <v>0.09805493801403116</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>2.644107606179461e-05</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.02594384178519249</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6891404872762998</v>
+        <v>0.09805000155201671</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>1.212337291075954e-05</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.02669586986303329</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6891382748557606</v>
+        <v>0.09804560042341171</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.02686766907572746</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6891327331830303</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>8.184014912590811e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0273643359541893</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6891298846103283</v>
+        <v>0.09804098490273906</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02799998596310616</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6891242171800547</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02896421402692795</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6891245977151124</v>
+        <v>0.09804103333447362</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.03013568371534348</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6891248260361471</v>
+        <v>0.0980412616555083</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.02914013713598251</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6891249159807971</v>
+        <v>0.09804135160015826</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.02831597253680229</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6891240580472122</v>
+        <v>0.09804049366657343</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.02776661887764931</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6891242863682469</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02685900405049324</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6891234907040351</v>
+        <v>0.09803992632339639</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.02768982574343681</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6891235529734082</v>
+        <v>0.09803998859276948</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.02761011198163033</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6891235806486851</v>
+        <v>0.09804001626804634</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.02742842212319374</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6891237328627083</v>
+        <v>0.09804016848206963</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02742539718747139</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6891233869217467</v>
+        <v>0.09803982254110789</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.02737503871321678</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6891234630287583</v>
+        <v>0.09803989864811953</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.02765726298093796</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6891236290804199</v>
+        <v>0.09804006469978113</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.02761605381965637</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6891239888590199</v>
+        <v>0.09804042447838117</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.02781001478433609</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6891240096154776</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.02823613211512566</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6891241133977661</v>
+        <v>0.09804054901712737</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.02935190871357918</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6891243417188009</v>
+        <v>0.09804077733816206</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.0292452909052372</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6891242171800547</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.02931348234415054</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6891242448553315</v>
+        <v>0.09804068047469272</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.02871971949934959</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6891243002058854</v>
+        <v>0.09804073582524667</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.02919252961874008</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6891245631210161</v>
+        <v>0.09804099874037737</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.02885666489601135</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6891244800951853</v>
+        <v>0.09804091571454657</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.02883317694067955</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6891242725306086</v>
+        <v>0.0980407081499698</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02882536500692368</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1262105352954337</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6891242863682469</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.02869466319680214</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6891244247446316</v>
+        <v>0.09804086036399286</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02792620286345482</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.689124141073043</v>
+        <v>0.09804057669240422</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02753955125808716</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6891239681025623</v>
+        <v>0.09804040372192348</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.02689264342188835</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6891238643202737</v>
+        <v>0.09804029993963498</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.0273788794875145</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6891240096154776</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.02768230065703392</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6891242517741509</v>
+        <v>0.09804068739351211</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.02680306509137154</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6891240788036699</v>
+        <v>0.09804051442303113</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.02635925263166428</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.689123781294443</v>
+        <v>0.09804021691380418</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.02552236616611481</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6891237674568044</v>
+        <v>0.09804020307616564</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.0251111276447773</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6891234007593852</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.0249379500746727</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6891234007593852</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.02405762299895287</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6891233384900121</v>
+        <v>0.09803977410937334</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.02431761473417282</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6891232347077236</v>
+        <v>0.09803967032708484</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.02390794083476067</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6891230617372428</v>
+        <v>0.09803949735660408</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.0234358012676239</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6891231101689774</v>
+        <v>0.09803954578833864</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.0228925496339798</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6891227503903774</v>
+        <v>0.0980391860097386</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.02281379699707031</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.689122708877462</v>
+        <v>0.09803914449682319</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.02256746962666512</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6891227642280157</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.02275842800736427</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6891228195785696</v>
+        <v>0.09803925519793084</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.02244344726204872</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.689122861091485</v>
+        <v>0.09803929671084624</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.0219159759581089</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6891225912575349</v>
+        <v>0.09803902687689615</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.02188511937856674</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6891226466080889</v>
+        <v>0.0980390822274501</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.02188767865300179</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6891227919032927</v>
+        <v>0.098039227522654</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.0216917097568512</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6891227573091965</v>
+        <v>0.09803919292855776</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.02148048579692841</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.689122743471558</v>
+        <v>0.09803917909091921</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.02123498916625977</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6891228334162082</v>
+        <v>0.09803926903556939</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.02104776352643967</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6891231516818928</v>
+        <v>0.09803958730125403</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.02145210653543472</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6891229717925926</v>
+        <v>0.0980394074119539</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02132811024785042</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6891230133055081</v>
+        <v>0.09803944892486929</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.02115611732006073</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6891228264973888</v>
+        <v>0.09803926211675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.02126938104629517</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6891228956855813</v>
+        <v>0.0980393313049425</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.02076578512787819</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6891226950398234</v>
+        <v>0.09803913065918465</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.02086640521883965</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3299999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6891227365527388</v>
+        <v>0.09803917217210005</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.02074291929602623</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1262105352954337</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6891227642280157</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
   </sheetData>
